--- a/out/Attention-MambaAMT_repeat_2_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6958951686397941</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.668078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC45" t="n">
-        <v>-4.82660812799586e-05</v>
+        <v>-0.0001723517053502146</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05544845703518964</v>
+        <v>-0.1979990062510304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.295895168639794</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.295895168639794</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.1981713579563806</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.05562204818224337</v>
+        <v>-0.198315697674074</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4506403949157474</v>
+        <v>0.5190124960639116</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8465239877093755</v>
+        <v>0.8407063319306644</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0321080335231275</v>
+        <v>0.0369795679610723</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4593767831834795</v>
+        <v>0.3948199044609692</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05630642259494752</v>
+        <v>0.06484943416446522</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5398711365932841</v>
+        <v>0.4875271208276998</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06840596550365705</v>
+        <v>0.07878471563896124</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.620371030755878</v>
+        <v>0.5802406908193023</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01810193239723054</v>
+        <v>0.02084840972466449</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5880815937408717</v>
+        <v>0.5430522074079626</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01005648025311157</v>
+        <v>0.01158303702004675</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5900754548880253</v>
+        <v>0.5453493415262485</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02112892082383949</v>
+        <v>0.02433554890394523</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6222912487008851</v>
+        <v>0.5824530069201146</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008298120768300192</v>
+        <v>0.009557637337587271</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6177397080759092</v>
+        <v>0.577211842858136</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005908077643374218</v>
+        <v>0.006805043913664355</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6212547974287558</v>
+        <v>0.5812608233820619</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002322425514821349</v>
+        <v>0.002675477226521204</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6199866013045392</v>
+        <v>0.5798010663207287</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001315991084127115</v>
+        <v>0.001516374795838346</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6202949854913724</v>
+        <v>0.5801569604932897</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004988043999624587</v>
+        <v>0.0005751383999567705</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6199740045357484</v>
+        <v>0.5797881036352981</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002306055348910609</v>
+        <v>0.0002669372295237945</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6199371545471519</v>
+        <v>0.5797464270304926</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.138380649587527e-05</v>
+        <v>9.430101120553886e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6198688249979608</v>
+        <v>0.5796686716029831</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>2.457311660285814e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6198280652532389</v>
+        <v>0.579622614118302</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>9.78655830142907e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6198230451479038</v>
+        <v>0.5796175910343989</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6198190271035601</v>
+        <v>0.579613718406542</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>5.776969076452056e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6198165924333693</v>
+        <v>0.5796116502120383</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6198110751913796</v>
+        <v>0.57960605855203</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.668078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6198047511973717</v>
+        <v>0.5795997345580222</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6197993834087933</v>
+        <v>0.5795943667694438</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.619799420157285</v>
+        <v>0.5795944035179355</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6197995304027605</v>
+        <v>0.579594513763411</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6197996038997441</v>
+        <v>0.5795945872603946</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6197997876422032</v>
+        <v>0.5795947710028537</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6198013310788597</v>
+        <v>0.5795963144395102</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6198028010185328</v>
+        <v>0.5795977843791833</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6198040504672548</v>
+        <v>0.5795990338279053</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6198054101614522</v>
+        <v>0.5796003935221026</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6198032052519429</v>
+        <v>0.5795981886125934</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6198028010185328</v>
+        <v>0.5795977843791833</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.5795969391638713</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6198025070305981</v>
+        <v>0.5795974903912486</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6198021762941717</v>
+        <v>0.5795971596548222</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6198018823062372</v>
+        <v>0.5795968656668877</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.5795969391638713</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.619801514821319</v>
+        <v>0.5795964981819693</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6198014045758433</v>
+        <v>0.5795963879364938</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6198013678273516</v>
+        <v>0.5795963511880021</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.619801514821319</v>
+        <v>0.5795964981819693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6198010370909253</v>
+        <v>0.5795960204515758</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6198019925517125</v>
+        <v>0.579596975912363</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.5795969391638713</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6198016250667945</v>
+        <v>0.579596608427445</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6198020660486964</v>
+        <v>0.5795970494093469</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6198014413243353</v>
+        <v>0.5795964246849857</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6198012575818761</v>
+        <v>0.5795962409425266</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6198008533484661</v>
+        <v>0.5795958367091166</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6198000081331542</v>
+        <v>0.5795949914938047</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6197999713846625</v>
+        <v>0.579594954745313</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6198001183786297</v>
+        <v>0.5795951017392802</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6198000448816461</v>
+        <v>0.5795950282422966</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6198001183786297</v>
+        <v>0.5795951017392802</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6198001551271216</v>
+        <v>0.5795951384877721</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6198000448816461</v>
+        <v>0.5795950282422966</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.619800485863548</v>
+        <v>0.5795954692241985</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6198003756180724</v>
+        <v>0.5795953589787229</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6198003388695805</v>
+        <v>0.579595322230231</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6198002653725969</v>
+        <v>0.5795952487332474</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6198002286241052</v>
+        <v>0.5795952119847557</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6198000081331542</v>
+        <v>0.5795949914938047</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6197999346361706</v>
+        <v>0.5795949179968209</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6197998611391868</v>
+        <v>0.5795948444998373</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6197998978876789</v>
+        <v>0.5795948812483293</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6197997876422032</v>
+        <v>0.5795947710028537</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6197998978876789</v>
+        <v>0.5795948812483293</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6198001918756133</v>
+        <v>0.5795951752362638</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.295895168639794</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC45" t="n">
-        <v>-4.82660812799586e-05</v>
+        <v>-8.375842391815968e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05544845703518964</v>
+        <v>-0.09622234179373856</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.05549672311646957</v>
+        <v>-0.0963061002176567</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.05562204818224337</v>
+        <v>-0.09640024046314449</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4506403949157474</v>
+        <v>0.3385068832175308</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8465239877093755</v>
+        <v>0.5812634715833922</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0321080335231275</v>
+        <v>0.02411854435772439</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4593767831834795</v>
+        <v>0.290450674885611</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05630642259494752</v>
+        <v>0.04229570910616239</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5398711365932841</v>
+        <v>0.3509154998218987</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06840596550365705</v>
+        <v>0.05138429148038152</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.295895168639794</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.620371030755878</v>
+        <v>0.4113843492173431</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01810193239723054</v>
+        <v>0.01359740595621322</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5880815937408717</v>
+        <v>0.3871295958956752</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01005648025311157</v>
+        <v>0.007552941830240709</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5900754548880253</v>
+        <v>0.3886260922855572</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02112892082383949</v>
+        <v>0.01587134513459355</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6222912487008851</v>
+        <v>0.4128258216189724</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008298120768300192</v>
+        <v>0.006232029165219661</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6177397080759092</v>
+        <v>0.4094055286704646</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005908077643374218</v>
+        <v>0.004436707973071357</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6212547974287558</v>
+        <v>0.4120448311599828</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002322425514821349</v>
+        <v>0.001743963864113126</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6199866013045392</v>
+        <v>0.4110908677484214</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001315991084127115</v>
+        <v>0.0009876700795540981</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6202949854913724</v>
+        <v>0.4113212249084879</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004988043999624587</v>
+        <v>0.0003731468922795144</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6199740045357484</v>
+        <v>0.4110790550536837</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002306055348910609</v>
+        <v>0.0001722546313900037</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6199371545471519</v>
+        <v>0.4110501484408348</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.138380649587527e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6198688249979608</v>
+        <v>0.4109977250613065</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6198280652532389</v>
+        <v>0.4109659056250861</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6198230451479038</v>
+        <v>0.4109608907322453</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6198190271035601</v>
+        <v>0.4109566545631713</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6198165924333693</v>
+        <v>0.4109536706840657</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6198110751913796</v>
+        <v>0.4109482269390593</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6198047511973717</v>
+        <v>0.410942234205629</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6197993834087933</v>
+        <v>0.4109368664170506</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.619799420157285</v>
+        <v>0.4109369031655423</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6197995304027605</v>
+        <v>0.4109370134110178</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6197996038997441</v>
+        <v>0.4109370869080015</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6197997876422032</v>
+        <v>0.4109372706504606</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6198013310788597</v>
+        <v>0.4109388140871171</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6198028010185328</v>
+        <v>0.4109402840267902</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6198040504672548</v>
+        <v>0.4109415334755122</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6198054101614522</v>
+        <v>0.4109428931697095</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6198032052519429</v>
+        <v>0.4109406882602002</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6198028010185328</v>
+        <v>0.4109402840267902</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.4109394388114782</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6198025070305981</v>
+        <v>0.4109399900388555</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6198021762941717</v>
+        <v>0.410939659302429</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6198018823062372</v>
+        <v>0.4109393653144946</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.4109394388114782</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.619801514821319</v>
+        <v>0.4109389978295763</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6198014045758433</v>
+        <v>0.4109388875841007</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6198013678273516</v>
+        <v>0.410938850835609</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.619801514821319</v>
+        <v>0.4109389978295763</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6198010370909253</v>
+        <v>0.4109385200991826</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6198019925517125</v>
+        <v>0.4109394755599699</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6198019558032208</v>
+        <v>0.4109394388114782</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6198016250667945</v>
+        <v>0.4109391080750518</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6198020660486964</v>
+        <v>0.4109395490569537</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6198014413243353</v>
+        <v>0.4109389243325927</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6198012575818761</v>
+        <v>0.4109387405901335</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6198008533484661</v>
+        <v>0.4109383363567234</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6198000081331542</v>
+        <v>0.4109374911414115</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6197999713846625</v>
+        <v>0.4109374543929198</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6198001183786297</v>
+        <v>0.410937601386887</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6198000448816461</v>
+        <v>0.4109375278899034</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6198001183786297</v>
+        <v>0.410937601386887</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6198001551271216</v>
+        <v>0.4109376381353789</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6198000448816461</v>
+        <v>0.4109375278899034</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.619800485863548</v>
+        <v>0.4109379688718053</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6198003756180724</v>
+        <v>0.4109378586263298</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6198003388695805</v>
+        <v>0.4109378218778379</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6198002653725969</v>
+        <v>0.4109377483808543</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6198002286241052</v>
+        <v>0.4109377116323626</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6198000081331542</v>
+        <v>0.4109374911414115</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6197999346361706</v>
+        <v>0.4109374176444279</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6197998611391868</v>
+        <v>0.4109373441474443</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052217</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6197998978876789</v>
+        <v>0.4109373808959362</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6197997876422032</v>
+        <v>0.4109372706504606</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6197998978876789</v>
+        <v>0.4109373808959362</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6198001918756133</v>
+        <v>0.4109376748838706</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02824815735220909</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.03878678753972054</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.04999999999999971</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.07753495872020721</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0318923331797123</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.03030406311154366</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5120598689052216</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01375360786914825</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.002320010215044022</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.01919214427471161</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.006854061037302017</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.00917455181479454</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01992368325591087</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001140423119068146</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01104560121893883</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006943691521883011</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.02419581636786461</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.02060619741678238</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001254122704267502</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002580340951681137</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.004617474973201752</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01143551990389824</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001969002187252045</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01638522371649742</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.006575819104909897</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.02141043171286583</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0003270842134952545</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01202837750315666</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.005949739366769791</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01755506917834282</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0193120650947094</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.02656029537320137</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.05422089621424675</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.02097941935062408</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02024252340197563</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01970407739281654</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0004375949501991272</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.02940553799271584</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004420913755893707</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.01657290384173393</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.03068586811423302</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02520476654171944</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03380594775080681</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.04145977273583412</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.05415317043662071</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01454827561974525</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7120598689052217</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.375842391815968e-05</v>
+        <v>-0.0001100360487170983</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09622234179373856</v>
+        <v>-0.12641028560471</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01444822549819946</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.06278473138809204</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.02613985165953636</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.003343779593706131</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.009886648505926132</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01868059113621712</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0001300014555454254</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.03440284356474876</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001635942608118057</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01612574234604836</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01273049041628838</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01370840892195702</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.04070873185992241</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0963061002176567</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.05640283599495888</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09640024046314449</v>
+        <v>-0.1266173643318048</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3385068832175308</v>
+        <v>0.3489431141413338</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0057343989610672</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5812634715833922</v>
+        <v>0.5719393619867589</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02411854435772439</v>
+        <v>0.02486212361989686</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.05198636278510094</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.290450674885611</v>
+        <v>0.2721603110477198</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04229570910616239</v>
+        <v>0.04359969377885883</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.04563241079449654</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3509154998218987</v>
+        <v>0.3344894616600205</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05138429148038152</v>
+        <v>0.0529687906448737</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.00253678485751152</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4113843492173431</v>
+        <v>0.3968229439731233</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01359740595621322</v>
+        <v>0.01401686914813446</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01879478618502617</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3871295958956752</v>
+        <v>0.3718202645036364</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007552941830240709</v>
+        <v>0.00778590591267374</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.05328906700015068</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3886260922855572</v>
+        <v>0.3733630426374906</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01587134513459355</v>
+        <v>0.01636135365428294</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.003706131130456924</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4128258216189724</v>
+        <v>0.3983086969876501</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006232029165219661</v>
+        <v>0.006424589871485665</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01992205902934074</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4094055286704646</v>
+        <v>0.3947833019616425</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004436707973071357</v>
+        <v>0.004572977848750051</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003330990672111511</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4120448311599828</v>
+        <v>0.3975037148406133</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001743963864113126</v>
+        <v>0.001796921620868104</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0208294652402401</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4110908677484214</v>
+        <v>0.396520649803566</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009876700795540981</v>
+        <v>0.001018498342894287</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002183858305215836</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4113212249084879</v>
+        <v>0.396758316192206</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003731468922795144</v>
+        <v>0.0003848905845863316</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.004226256161928177</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4110790550536837</v>
+        <v>0.3965087808139608</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001722546313900037</v>
+        <v>0.0001777594336070846</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.001272730529308319</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4110501484408348</v>
+        <v>0.3964791317597192</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.958602354831795e-05</v>
+        <v>6.200799943137988e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0004991404712200165</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4109977250613065</v>
+        <v>0.3964252350159408</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.407943006636009e-05</v>
+        <v>1.455641581801909e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01551226899027824</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4109659056250861</v>
+        <v>0.3963927533622256</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01229991391301155</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4109608907322453</v>
+        <v>0.3963877377247428</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.03222605213522911</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4109566545631713</v>
+        <v>0.3963835015556689</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.004648718982934952</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4109536706840657</v>
+        <v>0.3963805176765632</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.001490436494350433</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4109482269390593</v>
+        <v>0.3963750739315569</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004906237125396729</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.410942234205629</v>
+        <v>0.3963690811981265</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.02029426023364067</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4109368664170506</v>
+        <v>0.3963637134095482</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.005744289606809616</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4109369031655423</v>
+        <v>0.3963637501580399</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02284359559416771</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4109370134110178</v>
+        <v>0.3963638604035154</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.02396579459309578</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4109370869080015</v>
+        <v>0.396363933900499</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.08217804133892059</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4109372706504606</v>
+        <v>0.3963641176429582</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.00278564915060997</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4109388140871171</v>
+        <v>0.3963656610796146</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01128695532679558</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4109402840267902</v>
+        <v>0.3963671310192877</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.009008657187223434</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4109415334755122</v>
+        <v>0.3963683804680098</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.006396252661943436</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4109428931697095</v>
+        <v>0.3963697401622071</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01685801893472672</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4109406882602002</v>
+        <v>0.3963675352526977</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004090264439582825</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4109402840267902</v>
+        <v>0.3963671310192877</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.007620211690664291</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4109394388114782</v>
+        <v>0.3963662858039758</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01005050539970398</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4109399900388555</v>
+        <v>0.3963668370313531</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0009247995913028717</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.410939659302429</v>
+        <v>0.3963665062949266</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01097720488905907</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4109393653144946</v>
+        <v>0.3963662123069921</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.00737384706735611</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4109394388114782</v>
+        <v>0.3963662858039758</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.004061464220285416</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4109389978295763</v>
+        <v>0.3963658448220738</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.003185156732797623</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4109388875841007</v>
+        <v>0.3963657345765983</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01592643931508064</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.410938850835609</v>
+        <v>0.3963656978281066</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.009031552821397781</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4109389978295763</v>
+        <v>0.3963658448220738</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02008491382002831</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4109385200991826</v>
+        <v>0.3963653670916802</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.005011681467294693</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4109394755599699</v>
+        <v>0.3963663225524675</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02083796262741089</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4109394388114782</v>
+        <v>0.3963662858039758</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.00762094184756279</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4109391080750518</v>
+        <v>0.3963659550675493</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.007609274238348007</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4109395490569537</v>
+        <v>0.3963663960494513</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007701948285102844</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4109389243325927</v>
+        <v>0.3963657713250902</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01177691295742989</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4109387405901335</v>
+        <v>0.396365587582631</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02341349050402641</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4109383363567234</v>
+        <v>0.396365183349221</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001506324857473373</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4109374911414115</v>
+        <v>0.396364338133909</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005017828196287155</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4109374543929198</v>
+        <v>0.3963643013854173</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01861432567238808</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.410937601386887</v>
+        <v>0.3963644483793846</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.004298467189073563</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4109375278899034</v>
+        <v>0.3963643748824009</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.02907110378146172</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.410937601386887</v>
+        <v>0.3963644483793846</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01526283845305443</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4109376381353789</v>
+        <v>0.3963644851278765</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01876553520560265</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4109375278899034</v>
+        <v>0.3963643748824009</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01284875348210335</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4109379688718053</v>
+        <v>0.3963648158643029</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003784451633691788</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4109378586263298</v>
+        <v>0.3963647056188274</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005820054560899734</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4109378218778379</v>
+        <v>0.3963646688703354</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006215918809175491</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4109377483808543</v>
+        <v>0.3963645953733518</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01388683542609215</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4109377116323626</v>
+        <v>0.3963645586248601</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01543410494923592</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4109374911414115</v>
+        <v>0.396364338133909</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001974888145923615</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4109374176444279</v>
+        <v>0.3963642646369254</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00872170552611351</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4109373441474443</v>
+        <v>0.3963641911399418</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01278297230601311</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5120598689052217</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4109373808959362</v>
+        <v>0.3963642278884337</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.00327947735786438</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4109372706504606</v>
+        <v>0.3963641176429582</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02206609770655632</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8600000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4109373808959362</v>
+        <v>0.3963642278884337</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.003105964511632919</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8428995442101446</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4109376748838706</v>
+        <v>0.3963645218763682</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000008.xlsx
@@ -87599,7 +87599,7 @@
         <v>0.005017828196287155</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0.3963643013854173</v>
@@ -88394,7 +88394,7 @@
         <v>-0.01861432567238808</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
         <v>0.3963644483793846</v>
@@ -89189,7 +89189,7 @@
         <v>0.004298467189073563</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
         <v>0.3963643748824009</v>
@@ -89984,7 +89984,7 @@
         <v>0.02907110378146172</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
         <v>0.3963644483793846</v>
@@ -90779,7 +90779,7 @@
         <v>-0.01526283845305443</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC113" t="n">
         <v>0.3963644851278765</v>
@@ -93164,7 +93164,7 @@
         <v>0.003784451633691788</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
         <v>0.3963647056188274</v>
